--- a/StudentFinalPresentation/XLSFormat/A7135_PresentationList.xlsx
+++ b/StudentFinalPresentation/XLSFormat/A7135_PresentationList.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NeedDO\AZDNU\Projects\AI_Course\ai-management-course\StudentFinalPresentation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NeedDO\AZDNU\Projects\AI_Course\ai-management-course\StudentFinalPresentation\XLSFormat\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D0F96DE6-8CA8-41D2-A013-0D3197907972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85189052-11A6-47DA-9474-1599723429B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{589CEEDD-E764-410D-AB0D-4EA5C80B594A}"/>
   </bookViews>
@@ -1179,6 +1179,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B99B2AF8-2516-4F61-A2B9-F60F2D78D38D}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1649,6 +1652,7 @@
   <mergeCells count="1">
     <mergeCell ref="B1:D1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>